--- a/artfynd/A 30607-2022 artfynd.xlsx
+++ b/artfynd/A 30607-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 30607-2022 artfynd.xlsx
+++ b/artfynd/A 30607-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY3"/>
+  <dimension ref="A1:AY5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -675,56 +675,67 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>66640854</v>
+        <v>78283077</v>
       </c>
       <c r="B2" t="n">
-        <v>99611</v>
-      </c>
-      <c r="C2" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>43249</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E2" t="n">
-        <v>221343</v>
+        <v>101248</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Violett guldvinge</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Lycaena helle</t>
         </is>
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr"/>
-      <c r="J2" t="inlineStr"/>
-      <c r="K2" t="inlineStr"/>
-      <c r="L2" t="inlineStr"/>
+          <t>(Denis &amp; Schiffermüller, 1775)</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>imago/adult</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>friflygande</t>
+        </is>
+      </c>
       <c r="P2" t="inlineStr">
         <is>
-          <t>Lillkrogvägen-gamla riksvägen, Jmt</t>
+          <t>Lillkrogvägen gamla riksvägen, Jmt</t>
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>529266.5568866627</v>
+        <v>529240</v>
       </c>
       <c r="R2" t="n">
-        <v>6951058.473952882</v>
+        <v>6951058</v>
       </c>
       <c r="S2" t="n">
-        <v>50</v>
+        <v>25</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -748,27 +759,22 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2017-07-10</t>
+          <t>2019-06-07</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>00:00</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2017-07-10</t>
+          <t>2019-06-07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
         <is>
-          <t>00:00</t>
-        </is>
-      </c>
-      <c r="AC2" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>09:56</t>
         </is>
       </c>
       <c r="AD2" t="b">
@@ -798,16 +804,11 @@
         <v>66640903</v>
       </c>
       <c r="B3" t="n">
-        <v>44330</v>
-      </c>
-      <c r="C3" t="inlineStr">
-        <is>
-          <t>Ovaliderad</t>
-        </is>
+        <v>45044</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E3" t="n">
@@ -840,10 +841,10 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>529266.5568866627</v>
+        <v>529267</v>
       </c>
       <c r="R3" t="n">
-        <v>6951058.473952882</v>
+        <v>6951058</v>
       </c>
       <c r="S3" t="n">
         <v>50</v>
@@ -873,19 +874,9 @@
           <t>2017-07-10</t>
         </is>
       </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>00:00</t>
-        </is>
-      </c>
       <c r="AA3" t="inlineStr">
         <is>
           <t>2017-07-10</t>
-        </is>
-      </c>
-      <c r="AB3" t="inlineStr">
-        <is>
-          <t>00:00</t>
         </is>
       </c>
       <c r="AC3" t="inlineStr">
@@ -914,6 +905,208 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+    </row>
+    <row r="4">
+      <c r="A4" t="n">
+        <v>125908069</v>
+      </c>
+      <c r="B4" t="n">
+        <v>99035</v>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E4" t="n">
+        <v>219790</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Fläcknycklar</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>Dactylorhiza maculata</t>
+        </is>
+      </c>
+      <c r="H4" t="inlineStr">
+        <is>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I4" t="inlineStr"/>
+      <c r="P4" t="inlineStr">
+        <is>
+          <t>Lillkrogvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q4" t="n">
+        <v>529307</v>
+      </c>
+      <c r="R4" t="n">
+        <v>6951183</v>
+      </c>
+      <c r="S4" t="n">
+        <v>25</v>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V4" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W4" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AA4" t="inlineStr">
+        <is>
+          <t>2025-06-03</t>
+        </is>
+      </c>
+      <c r="AD4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG4" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT4" t="inlineStr"/>
+      <c r="AW4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX4" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY4" t="inlineStr"/>
+    </row>
+    <row r="5">
+      <c r="A5" t="n">
+        <v>66640854</v>
+      </c>
+      <c r="B5" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E5" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H5" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I5" t="inlineStr"/>
+      <c r="J5" t="inlineStr"/>
+      <c r="K5" t="inlineStr"/>
+      <c r="L5" t="inlineStr"/>
+      <c r="P5" t="inlineStr">
+        <is>
+          <t>Lillkrogvägen-gamla riksvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q5" t="n">
+        <v>529267</v>
+      </c>
+      <c r="R5" t="n">
+        <v>6951058</v>
+      </c>
+      <c r="S5" t="n">
+        <v>50</v>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V5" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W5" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y5" t="inlineStr">
+        <is>
+          <t>2017-07-10</t>
+        </is>
+      </c>
+      <c r="AA5" t="inlineStr">
+        <is>
+          <t>2017-07-10</t>
+        </is>
+      </c>
+      <c r="AC5" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG5" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT5" t="inlineStr"/>
+      <c r="AW5" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Håkan Blomqvist</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30607-2022 artfynd.xlsx
+++ b/artfynd/A 30607-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY5"/>
+  <dimension ref="A1:AY6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1005,51 +1005,56 @@
     </row>
     <row r="5">
       <c r="A5" t="n">
-        <v>66640854</v>
+        <v>134484641</v>
       </c>
       <c r="B5" t="n">
-        <v>102464</v>
+        <v>99112</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E5" t="n">
-        <v>221343</v>
+        <v>219790</v>
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>Brunklöver</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
         <is>
-          <t>Trifolium spadiceum</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
       <c r="J5" t="inlineStr"/>
-      <c r="K5" t="inlineStr"/>
+      <c r="K5" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
       <c r="L5" t="inlineStr"/>
+      <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillkrogvägen-gamla riksvägen, Jmt</t>
+          <t>Lillkrogen, längs vägen till, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
-        <v>529267</v>
+        <v>529262</v>
       </c>
       <c r="R5" t="n">
-        <v>6951058</v>
+        <v>6951065</v>
       </c>
       <c r="S5" t="n">
-        <v>50</v>
+        <v>10</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>
@@ -1073,17 +1078,12 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2017-07-10</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2017-07-10</t>
-        </is>
-      </c>
-      <c r="AC5" t="inlineStr">
-        <is>
-          <t>rikligt</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AD5" t="b">
@@ -1092,21 +1092,127 @@
       <c r="AE5" t="b">
         <v>0</v>
       </c>
+      <c r="AF5" t="inlineStr"/>
       <c r="AG5" t="b">
         <v>0</v>
       </c>
       <c r="AT5" t="inlineStr"/>
       <c r="AW5" t="inlineStr">
         <is>
+          <t>Lars Erik Norbäck</t>
+        </is>
+      </c>
+      <c r="AX5" t="inlineStr">
+        <is>
+          <t>Lars Erik Norbäck</t>
+        </is>
+      </c>
+      <c r="AY5" t="inlineStr"/>
+    </row>
+    <row r="6">
+      <c r="A6" t="n">
+        <v>66640854</v>
+      </c>
+      <c r="B6" t="n">
+        <v>102464</v>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>NT</t>
+        </is>
+      </c>
+      <c r="E6" t="n">
+        <v>221343</v>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>Brunklöver</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>Trifolium spadiceum</t>
+        </is>
+      </c>
+      <c r="H6" t="inlineStr">
+        <is>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I6" t="inlineStr"/>
+      <c r="J6" t="inlineStr"/>
+      <c r="K6" t="inlineStr"/>
+      <c r="L6" t="inlineStr"/>
+      <c r="P6" t="inlineStr">
+        <is>
+          <t>Lillkrogvägen-gamla riksvägen, Jmt</t>
+        </is>
+      </c>
+      <c r="Q6" t="n">
+        <v>529267</v>
+      </c>
+      <c r="R6" t="n">
+        <v>6951058</v>
+      </c>
+      <c r="S6" t="n">
+        <v>50</v>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="U6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="V6" t="inlineStr">
+        <is>
+          <t>Jämtland</t>
+        </is>
+      </c>
+      <c r="W6" t="inlineStr">
+        <is>
+          <t>Bräcke</t>
+        </is>
+      </c>
+      <c r="Y6" t="inlineStr">
+        <is>
+          <t>2017-07-10</t>
+        </is>
+      </c>
+      <c r="AA6" t="inlineStr">
+        <is>
+          <t>2017-07-10</t>
+        </is>
+      </c>
+      <c r="AC6" t="inlineStr">
+        <is>
+          <t>rikligt</t>
+        </is>
+      </c>
+      <c r="AD6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG6" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT6" t="inlineStr"/>
+      <c r="AW6" t="inlineStr">
+        <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
+      <c r="AX6" t="inlineStr">
         <is>
           <t>Håkan Blomqvist</t>
         </is>
       </c>
-      <c r="AY5" t="inlineStr"/>
+      <c r="AY6" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/A 30607-2022 artfynd.xlsx
+++ b/artfynd/A 30607-2022 artfynd.xlsx
@@ -1044,7 +1044,7 @@
       <c r="N5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Lillkrogen, längs vägen till, Jmt</t>
+          <t>Lillkrogen, vid vägkorsning SSV om, Jmt</t>
         </is>
       </c>
       <c r="Q5" t="n">
@@ -1054,7 +1054,7 @@
         <v>6951065</v>
       </c>
       <c r="S5" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T5" t="inlineStr">
         <is>

--- a/artfynd/A 30607-2022 artfynd.xlsx
+++ b/artfynd/A 30607-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY6"/>
+  <dimension ref="A1:AZ6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/78283077</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -905,6 +915,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66640903</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1002,6 +1017,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125908069</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1108,6 +1128,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134484641</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1213,8 +1238,20 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/66640854</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>